--- a/output/pdf_financials_xlsx/LRA.xlsx
+++ b/output/pdf_financials_xlsx/LRA.xlsx
@@ -5368,43 +5368,43 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>8.251113</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.181635</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>8.202304</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>8.339445</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>8.349246000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>9.054746</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>9.194039</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.2386</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>9.811222000000001</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>9.811222000000001</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>10.853332</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.863668</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.305046</v>
       </c>
     </row>
     <row r="93">
@@ -5889,37 +5889,37 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.078277</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.047051</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.029399</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>-0.002307</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.010965</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.017041</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.039699</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>0.036997</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.007681</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.005353</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.120293</v>
       </c>
       <c r="M103" s="3" t="n">
         <v>0.11082</v>
@@ -8945,7 +8945,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10014,7 +10018,11 @@
           <t>Prepaids and deposit (Note 5)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -10759,7 +10767,11 @@
           <t>Share-based payments reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -11285,7 +11297,11 @@
           <t>Prepaids and deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -11370,7 +11386,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -11878,7 +11898,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -14050,7 +14074,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -15411,7 +15439,11 @@
           <t>Prepaids and deposits 102,458</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E90" s="5" t="n">
         <v>0.071232</v>
       </c>
@@ -22873,7 +22905,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E174" s="5" t="n">
         <v>-0.078277</v>
       </c>

--- a/output/pdf_financials_xlsx/LRA.xlsx
+++ b/output/pdf_financials_xlsx/LRA.xlsx
@@ -1003,31 +1003,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003741</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008130999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.020238</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.042328</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.012314</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00298</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.015148</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.018618</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.00805</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.296657</v>
+        <v>-3.300398</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.365461</v>
+        <v>-3.373592</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.790004</v>
+        <v>-2.810242</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.369834</v>
+        <v>-4.412162</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.556354</v>
+        <v>-2.568668</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.145272</v>
+        <v>-2.148252</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.638341</v>
+        <v>-0.653489</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.177546</v>
+        <v>-1.196164</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.079196</v>
+        <v>-3.087246</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.15369</v>
@@ -1949,31 +1949,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.234965</v>
+        <v>-3.238706</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.348843</v>
+        <v>-3.356974</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.775426</v>
+        <v>-2.795664</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.365191</v>
+        <v>-4.407519</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.555233</v>
+        <v>-2.567547</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.144148</v>
+        <v>-2.147128</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.637644</v>
+        <v>-0.652792</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.176854</v>
+        <v>-1.195472</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.078504</v>
+        <v>-3.086554</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.152851</v>
@@ -2266,7 +2266,7 @@
         <v>5.144036</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.725873</v>
       </c>
     </row>
     <row r="35">
@@ -2370,7 +2370,7 @@
         <v>5.144036</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>2.725873</v>
       </c>
     </row>
     <row r="37">
@@ -2994,7 +2994,7 @@
         <v>0.09221699999999999</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.828037</v>
+        <v>0.102164</v>
       </c>
     </row>
     <row r="49">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -40465,7 +40465,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -45995,7 +45995,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -47627,7 +47627,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -49451,7 +49451,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E472" s="5" t="n">

--- a/output/pdf_financials_xlsx/LRA.xlsx
+++ b/output/pdf_financials_xlsx/LRA.xlsx
@@ -733,25 +733,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.225479</v>
+        <v>0.437479</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.181489</v>
+        <v>0.430246</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.147566</v>
+        <v>0.463226</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.111044</v>
+        <v>0.434418</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.08734500000000001</v>
+        <v>0.42161</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.062234</v>
+        <v>0.206771</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.142052</v>
+        <v>0.262052</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0.270095</v>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.055127</v>
+        <v>-0.054839</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.000543</v>
+        <v>-0.000124</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-1.672209150057164</v>
+        <v>-1.663473027372881</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0.01613449093601144</v>
+        <v>-0.003684487801225449</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -6305,40 +6305,40 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010826</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009526</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00543</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007556</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001832</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002555</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000343</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.058518</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007485</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006884</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007651</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015923</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -6519,16 +6519,16 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.497539</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.09983499999999999</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>1.0168</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -7545,40 +7545,40 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010826</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009526</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00543</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007556</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001832</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002555</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000343</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.058518</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007485</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006884</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007651</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015923</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.582637</v>
+        <v>-2.588067</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-2.180716</v>
+        <v>-2.188272</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.626338</v>
+        <v>-1.62817</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.952775</v>
+        <v>-0.953118</v>
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-1.533984</v>
+        <v>-1.541469</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.5652509999999999</v>
+        <v>-0.5721349999999999</v>
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-2.700471</v>
+        <v>-2.716394</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-2.262836</v>
@@ -21770,7 +21770,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -21861,7 +21865,11 @@
           <t>Shares issued in private placement</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -22225,7 +22233,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -23318,7 +23330,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -23476,7 +23492,11 @@
           <t>Shares issued in private placement</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -24785,7 +24805,11 @@
           <t>Shares issued for private placement</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -29129,7 +29153,11 @@
           <t>Proceeds from sale of AFS investments</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -30385,7 +30413,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -30472,7 +30504,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -31273,7 +31309,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -31914,7 +31954,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -32628,7 +32672,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E283" s="5" t="n">
         <v>-0.010826</v>
       </c>
@@ -34167,7 +34215,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E300" s="5" t="n">
         <v>-0.000288</v>
       </c>
@@ -40981,7 +41033,11 @@
           <t>Management and directors’ fees (Note 14)</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -42421,7 +42477,11 @@
           <t>Management and directors’ fees (Note 13)</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -44205,7 +44265,11 @@
           <t>Management and directors’ fees (Note 12)</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -45550,7 +45614,11 @@
           <t>Management and directors’ fees</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E429" s="5" t="n">
         <v>0.212</v>
       </c>
@@ -48355,7 +48423,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -48446,7 +48518,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -50268,7 +50344,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E481" s="5" t="n">
         <v>0.054839</v>
       </c>
@@ -50357,7 +50437,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E482" s="5" t="n">
         <v>0.000288</v>
       </c>
